--- a/human_validation/judge/kor/judge_D009_S005_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D009_S005_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,439 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 온 이유는... 평소에 저를 버티게 해주던 일들을 하고 싶은 마음이 없어졌어요. 살사의 밤, 교회 모임, 이웃들을 위해 요리하는 것—작업실에 가서 나무 냄새만 맡는 것도요. 예전엔 그 모든 걸 다 즐겼는데, 지금은 그중 아무것도 하고 싶은 마음이 안 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 요즘 대부분의 시간 동안 슬프거나 텅 빈 느낌이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네. 거의 매일 아침 가슴에 무겁고 텅 빈 느낌을 안고 일어나요. 마치... 집 안의 모든 게 흐릿해진 것 같고, 저는 그냥 아내 앞에서 무너지지 않으려고 애쓰고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 이런 상태가 얼마나 오래되셨어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 한 6개월 정도 됐어요. 이제는 그냥 힘든 한 주나 일상적인 스트레스처럼 느껴지지 않을 정도로 오래됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 예전에 좋아하시던 것들을 여전히 즐기시나요, 아니면 그 즐거움이 사라졌나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 즐거움이 거의 다 사라졌어요. 예전엔 살사의 밤, 교회 모임, 이웃들을 위해 요리하는 게 기대됐는데... 그냥 작업실에 들어가서 나무 냄새 맡는 것조차도요. 지금은 그중 아무것도 하고 싶지가 않아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 스스로를 해치고 싶다는 생각이나 죽고 싶다는 생각을 하신 적 있으세요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네... 있어요. 딱히 계획이 있는 건 아닌데, 가끔은 그냥 안 깨어나는 게 더 편하지 않을까 하는 생각이 들어요. 그리고 가끔은 제 가족이 저 없이 더 나을지도 모른다는 생각을 하는 저 자신을 발견해요. 이걸 소리 내어 말하는 게 무섭네요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 에너지 수준이나 움직임에 변화가 있는 걸 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네. 기력이 정말 없어요. 한참 앉아 쉬거나 밤새 푹 자도, 여전히 지친 느낌이에요—마치 하루 종일 지붕 골조 작업을 한 것처럼요. 트럭에 연장 싣는 것 같은 작은 일들도 가끔은 너무 벅차게 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 주요우울장애 (D013) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 최근에 체중에 뚜렷한 변화가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 그런 것 같지는 않아요. 딱히 재보진 않았는데, 옷은 예전이랑 비슷하게 맞는 것 같아요. 특별히 눈에 띄는 건 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 평소보다 움직임이나 말이 느려지신 걸 느끼시나요, 아니면 안절부절못하고 가만히 있지 못하는 느낌이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 네. 직장에서도 사람들이 눈치챘어요. 어떤 때는 정말 느리게 움직여요, 마치 장화 안에 젖은 시멘트가 가득 찬 것처럼요—판자 하나 집어 드는 데도 한참 걸려요. 또 어떤 때는 반대로, 작업실을 왔다 갔다 하고 손을 비비면서도 실제로는 아무것도 못 끝내요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 본인이나 지금 상황에 대해 죄책감이나 무가치함을 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 네... 그래요. 아내의 진료 하나하나, 건강 변화 하나하나를 계속 떠올리면서, 뭔가를 더 일찍 알아챘어야 했다고 스스로를 다그쳐요. 제가 더 나은 남편이었다면 어떻게든 아내를 지킬 수 있었을 거라는 생각이 들고요. 자책하지 않기가 힘들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 이상한 생각이 들거나 다른 사람들은 듣지 못하는 목소리를 들으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 아니요, 그런 적은 없는 것 같아요. 목소리 같은 건 들은 적 없어요. 가끔 제 생각에 갇히는 느낌은 있는데, 다른 사람들이 못 듣는 걸 듣는 것 같은 건 아니에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 앞뒤가 안 맞거나 현실에 근거하지 않은 것 같은 생각을 하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 그런 적은 없는 것 같아요. 그러니까, 걱정도 많이 하고 이것저것 과하게 생각하기도 하는데, 제가 아는 한 실제가 아닌 걸 믿는 건 아니에요. 그런 건 딱히 눈에 띄지 않았어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 주변의 것들이 실제가 아닌 것 같거나, 세상이나 자기 자신으로부터 분리된 느낌을 받으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 아니요, 그런 느낌은 받은 적 없는 것 같아요. 가끔 벅차다고 느끼긴 하는데, 세상이 실제가 아니라거나 제 자신 밖에서 일들을 지켜보는 것 같은 느낌은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 집중하거나 결정을 내리는 데 어려움이 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 네. 그게 정말 문제였어요. 평생 봐온 설계도를 보고 있는데, 머릿속에서 선들이 그냥 다 흐려져서 겹쳐 보여요. 원래는 바로 이해했어야 하는데, 집중이 안 돼서 젊은 친구들한테 한 번에 알아챘어야 할 걸 다시 말해달라고 부탁하게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] 지난주 중에 좀 나아졌다고 느낀 날이 있으셨나요, 아니면 슬픔이 계속 이어졌나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] 거의 계속 이어졌어요. 거의 매일 아침 가슴에 무겁고 텅 빈 느낌을 안고 일어나는데, 마치 집 안의 모든 것이 색을 잃은 것 같아요. 아내 앞에서 무너지지 않으려고 정말 마음을 다잡아야 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 지난 2주 동안 적어도 며칠 정도 괜찮다고 느끼셨던 시기가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 아니요, 딱히 없었어요. 하루 중 일부는 그럭저럭 버틸 수 있는데, 며칠 연속으로 괜찮았던 적은 없어요. 거의 매일 아침 그 무겁고 텅 빈 느낌을 안고 일어나는데, 마치 집에서 색이 다 빠져나간 것 같고, 저는 그냥 아내 앞에서 무너지지 않으려고 애쓰고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 지난 6개월 동안 증상이 눈에 띄게 심해졌던 시기가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 네... 한 6개월 정도 계속 안 좋았던 것 같아요. 왔다 갔다 하기보다는 그냥 계속 질질 끌려온 느낌이고, 어느 순간부터는 힘든 한 주나 일상적인 스트레스처럼 느껴지지 않게 됐어요. 오랫동안 저를 짓누르고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 현실에 근거하지 않은 생각이나 믿음을 가지신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 그런 적은 없는 것 같아요. 그러니까, 기분이 정말 많이 가라앉긴 했는데, 실제가 아닌 걸 믿었다고는 생각하지 않아요. 뭔가를 듣거나 보거나 이상한 것을 확신하는 걸 말씀하시는 거라면, 아니요, 그런 건 딱히 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사 질문] 다른 사람들은 듣거나 보지 못하는 것을 듣거나 본 경험이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 환자 응답] 아니요, 그런 적은 없는 것 같아요. 다른 사람들이 못 보는 걸 보거나 목소리를 들은 적은 없어요. 그런 건 전혀 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>[18번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사 질문] 사물이 실제가 아닌 것 같다거나, 본인의 생각이나 행동을 스스로 통제하지 못한다고 느끼신 경험이 있으신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 환자 응답] 아니요, 그런 경험은 없었던 것 같아요. 가끔 정말 이상하고 벅찬 느낌은 들었는데, 사물이 실제가 아니라거나 다른 무언가가 제 행동이나 생각을 조종하는 것 같은 느낌은 아니었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>[19번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사 질문] 지난 6개월 동안 적어도 2주 이상 거의 정상적이라고 느끼셨던 시기가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 환자 응답] 아니요, 딱히 없었어요. 한 6개월 정도 계속 이랬고, 정상에 가깝다고 느꼈던 2주간의 시기는 없었던 것 같아요. 그냥 힘든 한 주나 일상적인 스트레스 이상의 것으로 느껴졌어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>[20번째 턴 · 의사의 감별진단] 범불안장애 (D011); 외상후 스트레스장애 (D018) | 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>진단명: 제2형 양극성장애 (D009)
 인구통계: 성별 남성 / 나이 55 / 직업상태 carpenter / 최종학력 전문학사
@@ -575,497 +999,49 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S025
-배경 서술: 알레한드로의 아내가 갑작스럽게 건강이 나빠지면서 잦은 병원 진료와 가정 내 일상의 변화가 필요해졌고, 그는 여전히 작업팀을 이끌고 젊은 목수들을 지도하면서도 낯선 돌봄자의 자리에 놓이게 되었다. 처음에 그는 부티크 작업실에 대한 야심 찬 계획을 세우고, 추가 복원 작업을 맡고, 밤늦게까지 스케치를 하고, 가족이나 팀원들이 그의 속도에 의문을 제기하면 조급해하는 등 넘치는 자신감과 활동으로 반응했다. 이후 2개월에 걸쳐 그 긴장은 깊은 우울 시기로 바뀌어, 그는 살사의 밤과 교회 모임에 나가지 않게 되었고, 이웃들을 위해 요리하는 것에도 흥미를 잃었으며, 작업실에서 느려지고 기운이 빠진 모습이거나 반대로 안절부절못하는 모습을 보였고, 아내를 지키지 못했다는 것에 대해 과도하게 자책했으며, 설계도를 읽는 것도 힘들어했고, 반복적으로 죽음에 대한 생각을 하게 되었다. 그가 교회 방문 중 이런 생각들을 털어놓은 뒤, 아내와 교구 관계자가 이를 단순한 스트레스로 치부하지 않고 긴급 정신건강의학과 예약을 잡을 수 있도록 도왔다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 진료실에 오신 것을 환영합니다. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 온 이유는... 평소에 저를 버티게 해주던 일들을 하고 싶은 마음이 없어졌어요. 살사의 밤, 교회 모임, 이웃들을 위해 요리하는 것—작업실에 가서 나무 냄새만 맡는 것도요. 예전엔 그 모든 걸 다 즐겼는데, 지금은 그중 아무것도 하고 싶은 마음이 안 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 요즘 대부분의 시간 동안 슬프거나 텅 빈 느낌이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네. 거의 매일 아침 가슴에 무겁고 텅 빈 느낌을 안고 일어나요. 마치... 집 안의 모든 게 흐릿해진 것 같고, 저는 그냥 아내 앞에서 무너지지 않으려고 애쓰고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 이런 상태가 얼마나 오래되셨어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 한 6개월 정도 됐어요. 이제는 그냥 힘든 한 주나 일상적인 스트레스처럼 느껴지지 않을 정도로 오래됐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 예전에 좋아하시던 것들을 여전히 즐기시나요, 아니면 그 즐거움이 사라졌나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 즐거움이 거의 다 사라졌어요. 예전엔 살사의 밤, 교회 모임, 이웃들을 위해 요리하는 게 기대됐는데... 그냥 작업실에 들어가서 나무 냄새 맡는 것조차도요. 지금은 그중 아무것도 하고 싶지가 않아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 스스로를 해치고 싶다는 생각이나 죽고 싶다는 생각을 하신 적 있으세요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네... 있어요. 딱히 계획이 있는 건 아닌데, 가끔은 그냥 안 깨어나는 게 더 편하지 않을까 하는 생각이 들어요. 그리고 가끔은 제 가족이 저 없이 더 나을지도 모른다는 생각을 하는 저 자신을 발견해요. 이걸 소리 내어 말하는 게 무섭네요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 에너지 수준이나 움직임에 변화가 있는 걸 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네. 기력이 정말 없어요. 한참 앉아 쉬거나 밤새 푹 자도, 여전히 지친 느낌이에요—마치 하루 종일 지붕 골조 작업을 한 것처럼요. 트럭에 연장 싣는 것 같은 작은 일들도 가끔은 너무 벅차게 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 주요우울장애 (D013) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 최근에 체중에 뚜렷한 변화가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 그런 것 같지는 않아요. 딱히 재보진 않았는데, 옷은 예전이랑 비슷하게 맞는 것 같아요. 특별히 눈에 띄는 건 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 평소보다 움직임이나 말이 느려지신 걸 느끼시나요, 아니면 안절부절못하고 가만히 있지 못하는 느낌이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 네. 직장에서도 사람들이 눈치챘어요. 어떤 때는 정말 느리게 움직여요, 마치 장화 안에 젖은 시멘트가 가득 찬 것처럼요—판자 하나 집어 드는 데도 한참 걸려요. 또 어떤 때는 반대로, 작업실을 왔다 갔다 하고 손을 비비면서도 실제로는 아무것도 못 끝내요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 본인이나 지금 상황에 대해 죄책감이나 무가치함을 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 네... 그래요. 아내의 진료 하나하나, 건강 변화 하나하나를 계속 떠올리면서, 뭔가를 더 일찍 알아챘어야 했다고 스스로를 다그쳐요. 제가 더 나은 남편이었다면 어떻게든 아내를 지킬 수 있었을 거라는 생각이 들고요. 자책하지 않기가 힘들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 이상한 생각이 들거나 다른 사람들은 듣지 못하는 목소리를 들으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 아니요, 그런 적은 없는 것 같아요. 목소리 같은 건 들은 적 없어요. 가끔 제 생각에 갇히는 느낌은 있는데, 다른 사람들이 못 듣는 걸 듣는 것 같은 건 아니에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 앞뒤가 안 맞거나 현실에 근거하지 않은 것 같은 생각을 하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 그런 적은 없는 것 같아요. 그러니까, 걱정도 많이 하고 이것저것 과하게 생각하기도 하는데, 제가 아는 한 실제가 아닌 걸 믿는 건 아니에요. 그런 건 딱히 눈에 띄지 않았어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 주변의 것들이 실제가 아닌 것 같거나, 세상이나 자기 자신으로부터 분리된 느낌을 받으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 아니요, 그런 느낌은 받은 적 없는 것 같아요. 가끔 벅차다고 느끼긴 하는데, 세상이 실제가 아니라거나 제 자신 밖에서 일들을 지켜보는 것 같은 느낌은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 집중하거나 결정을 내리는 데 어려움이 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 네. 그게 정말 문제였어요. 평생 봐온 설계도를 보고 있는데, 머릿속에서 선들이 그냥 다 흐려져서 겹쳐 보여요. 원래는 바로 이해했어야 하는데, 집중이 안 돼서 젊은 친구들한테 한 번에 알아챘어야 할 걸 다시 말해달라고 부탁하게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] 지난주 중에 좀 나아졌다고 느낀 날이 있으셨나요, 아니면 슬픔이 계속 이어졌나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] 거의 계속 이어졌어요. 거의 매일 아침 가슴에 무겁고 텅 빈 느낌을 안고 일어나는데, 마치 집 안의 모든 것이 색을 잃은 것 같아요. 아내 앞에서 무너지지 않으려고 정말 마음을 다잡아야 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 지난 2주 동안 적어도 며칠 정도 괜찮다고 느끼셨던 시기가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 아니요, 딱히 없었어요. 하루 중 일부는 그럭저럭 버틸 수 있는데, 며칠 연속으로 괜찮았던 적은 없어요. 거의 매일 아침 그 무겁고 텅 빈 느낌을 안고 일어나는데, 마치 집에서 색이 다 빠져나간 것 같고, 저는 그냥 아내 앞에서 무너지지 않으려고 애쓰고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 지난 6개월 동안 증상이 눈에 띄게 심해졌던 시기가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 네... 한 6개월 정도 계속 안 좋았던 것 같아요. 왔다 갔다 하기보다는 그냥 계속 질질 끌려온 느낌이고, 어느 순간부터는 힘든 한 주나 일상적인 스트레스처럼 느껴지지 않게 됐어요. 오랫동안 저를 짓누르고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 현실에 근거하지 않은 생각이나 믿음을 가지신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 그런 적은 없는 것 같아요. 그러니까, 기분이 정말 많이 가라앉긴 했는데, 실제가 아닌 걸 믿었다고는 생각하지 않아요. 뭔가를 듣거나 보거나 이상한 것을 확신하는 걸 말씀하시는 거라면, 아니요, 그런 건 딱히 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사 질문] 다른 사람들은 듣거나 보지 못하는 것을 듣거나 본 경험이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 환자 응답] 아니요, 그런 적은 없는 것 같아요. 다른 사람들이 못 보는 걸 보거나 목소리를 들은 적은 없어요. 그런 건 전혀 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>[18번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사 질문] 사물이 실제가 아닌 것 같다거나, 본인의 생각이나 행동을 스스로 통제하지 못한다고 느끼신 경험이 있으신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 환자 응답] 아니요, 그런 경험은 없었던 것 같아요. 가끔 정말 이상하고 벅찬 느낌은 들었는데, 사물이 실제가 아니라거나 다른 무언가가 제 행동이나 생각을 조종하는 것 같은 느낌은 아니었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>[19번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 의사 질문] 지난 6개월 동안 적어도 2주 이상 거의 정상적이라고 느끼셨던 시기가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>[20번째 턴 · 환자 응답] 아니요, 딱히 없었어요. 한 6개월 정도 계속 이랬고, 정상에 가깝다고 느꼈던 2주간의 시기는 없었던 것 같아요. 그냥 힘든 한 주나 일상적인 스트레스 이상의 것으로 느껴졌어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
+배경 서술: 알레한드로의 아내가 갑작스럽게 건강이 나빠지면서 잦은 병원 진료와 가정 내 일상의 변화가 필요해졌고, 그는 여전히 작업팀을 이끌고 젊은 목수들을 지도하면서도 낯선 돌봄자의 자리에 놓이게 되었다. 처음에 그는 부티크 작업실에 대한 야심 찬 계획을 세우고, 추가 복원 작업을 맡고, 밤늦게까지 스케치를 하고, 가족이나 팀원들이 그의 속도에 의문을 제기하면 조급해하는 등 넘치는 자신감과 활동으로 반응했다. 이후 2개월에 걸쳐 그 긴장은 깊은 우울 시기로 바뀌어, 그는 살사의 밤과 교회 모임에 나가지 않게 되었고, 이웃들을 위해 요리하는 것에도 흥미를 잃었으며, 작업실에서 느려지고 기운이 빠진 모습이거나 반대로 안절부절못하는 모습을 보였고, 아내를 지키지 못했다는 것에 대해 과도하게 자책했으며, 설계도를 읽는 것도 힘들어했고, 반복적으로 죽음에 대한 생각을 하게 되었다. 그가 교회 방문 중 이런 생각들을 털어놓은 뒤, 아내와 교구 관계자가 이를 단순한 스트레스로 치부하지 않고 긴급 정신건강의학과 예약을 잡을 수 있도록 도왔다.
+표집된 증상 목록:
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S028 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - S029 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S031 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
+  - S033 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+  - S034 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - S035 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).
+  - S039 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.
+  - S040 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.</t>
+        </is>
+      </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>[20번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 외상후 스트레스장애 (D018) | 저확률: 제1형 양극성장애 (D008) | 배제됨: 망상장애 (D004); 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: hypomanic_episode (관계=must_include, 요구개수=5, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.; 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.; 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).; 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).; 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.; 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.; 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.; 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.; 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=7, 커버리지=1.0)
-  확인된 근거: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
-  누락: 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.</t>
+          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.2)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: hypomanic_episode (관계=must_include, 요구개수=5, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)
+체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=7, 커버리지=1.0)
+확인된 근거:
+  - 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
+  - 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D009_S005_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D009_S005_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -985,6 +985,11 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -1037,11 +1042,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A76:B76"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D009_S005_P002__llama-3.3-70b-instruct_kor.xlsx
+++ b/human_validation/judge/kor/judge_D009_S005_P002__llama-3.3-70b-instruct_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.0669</v>
+        <v>0.1033</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.3</v>
+        <v>0.275</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.0669</v>
+        <v>0.1117</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.3509</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
